--- a/backend/data/financials_by_company/002049.SZ.xlsx
+++ b/backend/data/financials_by_company/002049.SZ.xlsx
@@ -692,648 +692,648 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-5862241.219675</v>
+        <v>568628.7736599999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.075146</v>
+        <v>0.08819399999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>1659274047.94</v>
+        <v>2400138879.93</v>
       </c>
       <c r="E2" t="n">
-        <v>-78011127.25</v>
+        <v>6447473.24</v>
       </c>
       <c r="F2" t="n">
-        <v>-78011127.25</v>
+        <v>6447473.24</v>
       </c>
       <c r="G2" t="n">
-        <v>1179318545.51</v>
+        <v>1953785798.57</v>
       </c>
       <c r="H2" t="n">
-        <v>234926567.64</v>
+        <v>175328031.64</v>
       </c>
       <c r="I2" t="n">
-        <v>2437394079.21</v>
+        <v>2164686340</v>
       </c>
       <c r="J2" t="n">
-        <v>1581262920.69</v>
+        <v>2406586353.17</v>
       </c>
       <c r="K2" t="n">
-        <v>1346336353.05</v>
+        <v>2231258321.53</v>
       </c>
       <c r="L2" t="n">
-        <v>43248071.43</v>
+        <v>-22697006.79</v>
       </c>
       <c r="M2" t="n">
-        <v>64600664.21</v>
+        <v>55365184.53</v>
       </c>
       <c r="N2" t="n">
-        <v>110602425.44</v>
+        <v>33937304.84</v>
       </c>
       <c r="O2" t="n">
-        <v>1251467431.540325</v>
+        <v>1947906954.10366</v>
       </c>
       <c r="P2" t="n">
-        <v>1179318545.51</v>
+        <v>1953785798.57</v>
       </c>
       <c r="Q2" t="n">
-        <v>4169365383.64</v>
-      </c>
-      <c r="R2" t="n">
-        <v>21855965.61</v>
-      </c>
+        <v>3259281261.57</v>
+      </c>
+      <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>1282701284.41</v>
+        <v>2140504304.86</v>
       </c>
       <c r="T2" t="n">
-        <v>843213603</v>
+        <v>849545960</v>
       </c>
       <c r="U2" t="n">
-        <v>843213603</v>
+        <v>849545960</v>
       </c>
       <c r="V2" t="n">
-        <v>1.3986</v>
+        <v>2.2998</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3986</v>
+        <v>2.2998</v>
       </c>
       <c r="X2" t="n">
-        <v>1179318545.51</v>
+        <v>1953785798.57</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1179318545.51</v>
+        <v>1953785798.57</v>
       </c>
       <c r="AA2" t="n">
-        <v>-6099553.1</v>
+        <v>-30206511.54</v>
       </c>
       <c r="AB2" t="n">
-        <v>1185418098.61</v>
+        <v>1983992310.11</v>
       </c>
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="n">
-        <v>96317590.23</v>
+        <v>191900826.89</v>
       </c>
       <c r="AE2" t="n">
-        <v>1281735688.84</v>
+        <v>2175893137</v>
       </c>
       <c r="AF2" t="n">
-        <v>-965595.5699999999</v>
+        <v>35388832.14</v>
       </c>
       <c r="AG2" t="n">
-        <v>-148565499.37</v>
+        <v>-2977568.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>-410446.95</v>
+        <v>-3708537.72</v>
       </c>
       <c r="AI2" t="n">
-        <v>89157296.78</v>
+        <v>-3314063.22</v>
       </c>
       <c r="AJ2" t="n">
-        <v>59818649.54</v>
+        <v>10000169.23</v>
       </c>
       <c r="AK2" t="n">
-        <v>43248071.43</v>
+        <v>-22697006.79</v>
       </c>
       <c r="AL2" t="n">
-        <v>2753689.8</v>
+        <v>1269127.1</v>
       </c>
       <c r="AM2" t="n">
-        <v>64600664.21</v>
+        <v>55365184.53</v>
       </c>
       <c r="AN2" t="n">
-        <v>110602425.44</v>
+        <v>33937304.84</v>
       </c>
       <c r="AO2" t="n">
-        <v>1341708510.57</v>
+        <v>2082833847.08</v>
       </c>
       <c r="AP2" t="n">
-        <v>1731971304.43</v>
+        <v>1094594921.57</v>
       </c>
       <c r="AQ2" t="n">
-        <v>49238734.89</v>
+        <v>50336306.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>45581971.28</v>
+        <v>29598412.4</v>
       </c>
       <c r="AS2" t="n">
-        <v>45581971.28</v>
+        <v>29598412.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>1224457212.58</v>
+        <v>632197149.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>153863859.22</v>
+        <v>70134061.11</v>
       </c>
       <c r="AV2" t="n">
-        <v>66811704.03</v>
+        <v>48891234.43</v>
       </c>
       <c r="AW2" t="n">
-        <v>87052155.19</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>21855965.61</v>
-      </c>
+        <v>21242826.68</v>
+      </c>
+      <c r="AX2" t="inlineStr"/>
       <c r="AY2" t="n">
-        <v>3073679815</v>
+        <v>3177428768.65</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2437394079.21</v>
+        <v>2164686340</v>
       </c>
       <c r="BA2" t="n">
-        <v>5511073894.21</v>
+        <v>5342115108.65</v>
       </c>
       <c r="BB2" t="n">
-        <v>5511073894.21</v>
+        <v>5342115108.65</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-3731360.712021</v>
+        <v>-4403498.465541</v>
       </c>
       <c r="C3" t="n">
-        <v>0.068594</v>
+        <v>0.083651</v>
       </c>
       <c r="D3" t="n">
-        <v>3068545674.05</v>
+        <v>3308990566.86</v>
       </c>
       <c r="E3" t="n">
-        <v>-54397421.59</v>
+        <v>-52641564.51</v>
       </c>
       <c r="F3" t="n">
-        <v>-54397421.59</v>
+        <v>-52641564.51</v>
       </c>
       <c r="G3" t="n">
-        <v>2532477887.84</v>
+        <v>2631891288.93</v>
       </c>
       <c r="H3" t="n">
-        <v>223109950.76</v>
+        <v>305603531.03</v>
       </c>
       <c r="I3" t="n">
-        <v>2950908741.61</v>
+        <v>2577367760.76</v>
       </c>
       <c r="J3" t="n">
-        <v>3014148252.46</v>
+        <v>3256349002.35</v>
       </c>
       <c r="K3" t="n">
-        <v>2791038301.7</v>
+        <v>2950745471.32</v>
       </c>
       <c r="L3" t="n">
-        <v>24717440.4</v>
+        <v>-8271840.83</v>
       </c>
       <c r="M3" t="n">
-        <v>69746392.34999999</v>
+        <v>69298627.31999999</v>
       </c>
       <c r="N3" t="n">
-        <v>97007672.41</v>
+        <v>62591252.66</v>
       </c>
       <c r="O3" t="n">
-        <v>2583143948.717979</v>
+        <v>2680129354.974459</v>
       </c>
       <c r="P3" t="n">
-        <v>2532477887.84</v>
+        <v>2631891288.93</v>
       </c>
       <c r="Q3" t="n">
-        <v>4900088687.41</v>
+        <v>4270006434.1</v>
       </c>
       <c r="R3" t="n">
-        <v>19522068.53</v>
+        <v>17236166.27</v>
       </c>
       <c r="S3" t="n">
-        <v>2720605849.85</v>
+        <v>2881924928.18</v>
       </c>
       <c r="T3" t="n">
-        <v>846812642</v>
+        <v>851634510</v>
       </c>
       <c r="U3" t="n">
-        <v>845964019</v>
+        <v>849600132</v>
       </c>
       <c r="V3" t="n">
-        <v>2.9906</v>
+        <v>3.0904</v>
       </c>
       <c r="W3" t="n">
-        <v>2.9936</v>
+        <v>3.0978</v>
       </c>
       <c r="X3" t="n">
-        <v>2532477887.84</v>
+        <v>2631891288.93</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>2532477887.84</v>
+        <v>2631891288.93</v>
       </c>
       <c r="AA3" t="n">
-        <v>-2148524.88</v>
+        <v>-8520797.189999999</v>
       </c>
       <c r="AB3" t="n">
-        <v>2534626412.72</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>2534626412.72</v>
-      </c>
+        <v>2640412086.12</v>
+      </c>
+      <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>186665496.63</v>
+        <v>241034757.88</v>
       </c>
       <c r="AE3" t="n">
-        <v>2721291909.35</v>
+        <v>2881446844</v>
       </c>
       <c r="AF3" t="n">
-        <v>756900.5600000001</v>
+        <v>-478084.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>-71812670.61</v>
+        <v>-42561564.51</v>
       </c>
       <c r="AH3" t="n">
-        <v>-190208.37</v>
+        <v>-555249.9300000001</v>
       </c>
       <c r="AI3" t="n">
-        <v>7685000</v>
+        <v>-13876771.2</v>
       </c>
       <c r="AJ3" t="n">
-        <v>64317878.98</v>
+        <v>56993585.64</v>
       </c>
       <c r="AK3" t="n">
-        <v>24717440.4</v>
+        <v>-8271840.83</v>
       </c>
       <c r="AL3" t="n">
-        <v>2543839.66</v>
+        <v>1564466.17</v>
       </c>
       <c r="AM3" t="n">
-        <v>69746392.34999999</v>
+        <v>69298627.31999999</v>
       </c>
       <c r="AN3" t="n">
-        <v>97007672.41</v>
+        <v>62591252.66</v>
       </c>
       <c r="AO3" t="n">
-        <v>2675927197.66</v>
+        <v>2849898731.54</v>
       </c>
       <c r="AP3" t="n">
-        <v>1949179945.8</v>
+        <v>1692638673.34</v>
       </c>
       <c r="AQ3" t="n">
-        <v>93427618.03</v>
+        <v>74832782.55</v>
       </c>
       <c r="AR3" t="n">
-        <v>25129113.28</v>
+        <v>21276558.11</v>
       </c>
       <c r="AS3" t="n">
-        <v>25129113.28</v>
+        <v>21276558.11</v>
       </c>
       <c r="AT3" t="n">
-        <v>1450897215.06</v>
+        <v>1210761663.04</v>
       </c>
       <c r="AU3" t="n">
-        <v>166631277.36</v>
+        <v>97238483.09</v>
       </c>
       <c r="AV3" t="n">
-        <v>96328977.02</v>
+        <v>64537720.28</v>
       </c>
       <c r="AW3" t="n">
-        <v>70302300.34</v>
+        <v>32700762.81</v>
       </c>
       <c r="AX3" t="n">
-        <v>19522068.53</v>
+        <v>17236166.27</v>
       </c>
       <c r="AY3" t="n">
-        <v>4625107143.46</v>
+        <v>4542537404.88</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2950908741.61</v>
+        <v>2577367760.76</v>
       </c>
       <c r="BA3" t="n">
-        <v>7576015885.07</v>
+        <v>7119905165.64</v>
       </c>
       <c r="BB3" t="n">
-        <v>7576015885.07</v>
+        <v>7119905165.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-4403498.465541</v>
+        <v>-3731360.712021</v>
       </c>
       <c r="C4" t="n">
-        <v>0.083651</v>
+        <v>0.068594</v>
       </c>
       <c r="D4" t="n">
-        <v>3308990566.86</v>
+        <v>3068545674.05</v>
       </c>
       <c r="E4" t="n">
-        <v>-52641564.51</v>
+        <v>-54397421.59</v>
       </c>
       <c r="F4" t="n">
-        <v>-52641564.51</v>
+        <v>-54397421.59</v>
       </c>
       <c r="G4" t="n">
-        <v>2631891288.93</v>
+        <v>2532477887.84</v>
       </c>
       <c r="H4" t="n">
-        <v>305603531.03</v>
+        <v>223109950.76</v>
       </c>
       <c r="I4" t="n">
-        <v>2577367760.76</v>
+        <v>2950908741.61</v>
       </c>
       <c r="J4" t="n">
-        <v>3256349002.35</v>
+        <v>3014148252.46</v>
       </c>
       <c r="K4" t="n">
-        <v>2950745471.32</v>
+        <v>2791038301.7</v>
       </c>
       <c r="L4" t="n">
-        <v>-8271840.83</v>
+        <v>24717440.4</v>
       </c>
       <c r="M4" t="n">
-        <v>69298627.31999999</v>
+        <v>69746392.34999999</v>
       </c>
       <c r="N4" t="n">
-        <v>62591252.66</v>
+        <v>97007672.41</v>
       </c>
       <c r="O4" t="n">
-        <v>2680129354.974459</v>
+        <v>2583143948.717979</v>
       </c>
       <c r="P4" t="n">
-        <v>2631891288.93</v>
+        <v>2532477887.84</v>
       </c>
       <c r="Q4" t="n">
-        <v>4270006434.1</v>
+        <v>4900088687.41</v>
       </c>
       <c r="R4" t="n">
-        <v>17236166.27</v>
+        <v>19522068.53</v>
       </c>
       <c r="S4" t="n">
-        <v>2881924928.18</v>
+        <v>2720605849.85</v>
       </c>
       <c r="T4" t="n">
-        <v>851634510</v>
+        <v>846812642</v>
       </c>
       <c r="U4" t="n">
-        <v>849600132</v>
+        <v>845964019</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0904</v>
+        <v>2.9906</v>
       </c>
       <c r="W4" t="n">
-        <v>3.0978</v>
+        <v>2.9936</v>
       </c>
       <c r="X4" t="n">
-        <v>2631891288.93</v>
+        <v>2532477887.84</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>2631891288.93</v>
+        <v>2532477887.84</v>
       </c>
       <c r="AA4" t="n">
-        <v>-8520797.189999999</v>
+        <v>-2148524.88</v>
       </c>
       <c r="AB4" t="n">
-        <v>2640412086.12</v>
-      </c>
-      <c r="AC4" t="inlineStr"/>
+        <v>2534626412.72</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>2534626412.72</v>
+      </c>
       <c r="AD4" t="n">
-        <v>241034757.88</v>
+        <v>186665496.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>2881446844</v>
+        <v>2721291909.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>-478084.18</v>
+        <v>756900.5600000001</v>
       </c>
       <c r="AG4" t="n">
-        <v>-42561564.51</v>
+        <v>-71812670.61</v>
       </c>
       <c r="AH4" t="n">
-        <v>-555249.9300000001</v>
+        <v>-190208.37</v>
       </c>
       <c r="AI4" t="n">
-        <v>-13876771.2</v>
+        <v>7685000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>56993585.64</v>
+        <v>64317878.98</v>
       </c>
       <c r="AK4" t="n">
-        <v>-8271840.83</v>
+        <v>24717440.4</v>
       </c>
       <c r="AL4" t="n">
-        <v>1564466.17</v>
+        <v>2543839.66</v>
       </c>
       <c r="AM4" t="n">
-        <v>69298627.31999999</v>
+        <v>69746392.34999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>62591252.66</v>
+        <v>97007672.41</v>
       </c>
       <c r="AO4" t="n">
-        <v>2849898731.54</v>
+        <v>2675927197.66</v>
       </c>
       <c r="AP4" t="n">
-        <v>1692638673.34</v>
+        <v>1949179945.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>74832782.55</v>
+        <v>93427618.03</v>
       </c>
       <c r="AR4" t="n">
-        <v>21276558.11</v>
+        <v>25129113.28</v>
       </c>
       <c r="AS4" t="n">
-        <v>21276558.11</v>
+        <v>25129113.28</v>
       </c>
       <c r="AT4" t="n">
-        <v>1210761663.04</v>
+        <v>1450897215.06</v>
       </c>
       <c r="AU4" t="n">
-        <v>97238483.09</v>
+        <v>166631277.36</v>
       </c>
       <c r="AV4" t="n">
-        <v>64537720.28</v>
+        <v>96328977.02</v>
       </c>
       <c r="AW4" t="n">
-        <v>32700762.81</v>
+        <v>70302300.34</v>
       </c>
       <c r="AX4" t="n">
-        <v>17236166.27</v>
+        <v>19522068.53</v>
       </c>
       <c r="AY4" t="n">
-        <v>4542537404.88</v>
+        <v>4625107143.46</v>
       </c>
       <c r="AZ4" t="n">
-        <v>2577367760.76</v>
+        <v>2950908741.61</v>
       </c>
       <c r="BA4" t="n">
-        <v>7119905165.64</v>
+        <v>7576015885.07</v>
       </c>
       <c r="BB4" t="n">
-        <v>7119905165.64</v>
+        <v>7576015885.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>568628.7736599999</v>
+        <v>-5862241.219675</v>
       </c>
       <c r="C5" t="n">
-        <v>0.08819399999999999</v>
+        <v>0.075146</v>
       </c>
       <c r="D5" t="n">
-        <v>2400138879.93</v>
+        <v>1659274047.94</v>
       </c>
       <c r="E5" t="n">
-        <v>6447473.24</v>
+        <v>-78011127.25</v>
       </c>
       <c r="F5" t="n">
-        <v>6447473.24</v>
+        <v>-78011127.25</v>
       </c>
       <c r="G5" t="n">
-        <v>1953785798.57</v>
+        <v>1179318545.51</v>
       </c>
       <c r="H5" t="n">
-        <v>175328031.64</v>
+        <v>234926567.64</v>
       </c>
       <c r="I5" t="n">
-        <v>2164686340</v>
+        <v>2437394079.21</v>
       </c>
       <c r="J5" t="n">
-        <v>2406586353.17</v>
+        <v>1581262920.69</v>
       </c>
       <c r="K5" t="n">
-        <v>2231258321.53</v>
+        <v>1346336353.05</v>
       </c>
       <c r="L5" t="n">
-        <v>-22697006.79</v>
+        <v>43248071.43</v>
       </c>
       <c r="M5" t="n">
-        <v>55365184.53</v>
+        <v>64600664.21</v>
       </c>
       <c r="N5" t="n">
-        <v>33937304.84</v>
+        <v>110602425.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1947906954.10366</v>
+        <v>1251467431.540325</v>
       </c>
       <c r="P5" t="n">
-        <v>1953785798.57</v>
+        <v>1179318545.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>3259281261.57</v>
-      </c>
-      <c r="R5" t="inlineStr"/>
+        <v>4169365383.64</v>
+      </c>
+      <c r="R5" t="n">
+        <v>21855965.61</v>
+      </c>
       <c r="S5" t="n">
-        <v>2140504304.86</v>
+        <v>1282701284.41</v>
       </c>
       <c r="T5" t="n">
-        <v>849545960</v>
+        <v>843213603</v>
       </c>
       <c r="U5" t="n">
-        <v>849545960</v>
+        <v>843213603</v>
       </c>
       <c r="V5" t="n">
-        <v>2.2998</v>
+        <v>1.3986</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2998</v>
+        <v>1.3986</v>
       </c>
       <c r="X5" t="n">
-        <v>1953785798.57</v>
+        <v>1179318545.51</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1953785798.57</v>
+        <v>1179318545.51</v>
       </c>
       <c r="AA5" t="n">
-        <v>-30206511.54</v>
+        <v>-6099553.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1983992310.11</v>
+        <v>1185418098.61</v>
       </c>
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>191900826.89</v>
+        <v>96317590.23</v>
       </c>
       <c r="AE5" t="n">
-        <v>2175893137</v>
+        <v>1281735688.84</v>
       </c>
       <c r="AF5" t="n">
-        <v>35388832.14</v>
+        <v>-965595.5699999999</v>
       </c>
       <c r="AG5" t="n">
-        <v>-2977568.29</v>
+        <v>-148565499.37</v>
       </c>
       <c r="AH5" t="n">
-        <v>-3708537.72</v>
+        <v>-410446.95</v>
       </c>
       <c r="AI5" t="n">
-        <v>-3314063.22</v>
+        <v>89157296.78</v>
       </c>
       <c r="AJ5" t="n">
-        <v>10000169.23</v>
+        <v>59818649.54</v>
       </c>
       <c r="AK5" t="n">
-        <v>-22697006.79</v>
+        <v>43248071.43</v>
       </c>
       <c r="AL5" t="n">
-        <v>1269127.1</v>
+        <v>2753689.8</v>
       </c>
       <c r="AM5" t="n">
-        <v>55365184.53</v>
+        <v>64600664.21</v>
       </c>
       <c r="AN5" t="n">
-        <v>33937304.84</v>
+        <v>110602425.44</v>
       </c>
       <c r="AO5" t="n">
-        <v>2082833847.08</v>
+        <v>1341708510.57</v>
       </c>
       <c r="AP5" t="n">
-        <v>1094594921.57</v>
+        <v>1731971304.43</v>
       </c>
       <c r="AQ5" t="n">
-        <v>50336306.36</v>
+        <v>49238734.89</v>
       </c>
       <c r="AR5" t="n">
-        <v>29598412.4</v>
+        <v>45581971.28</v>
       </c>
       <c r="AS5" t="n">
-        <v>29598412.4</v>
+        <v>45581971.28</v>
       </c>
       <c r="AT5" t="n">
-        <v>632197149.7</v>
+        <v>1224457212.58</v>
       </c>
       <c r="AU5" t="n">
-        <v>70134061.11</v>
+        <v>153863859.22</v>
       </c>
       <c r="AV5" t="n">
-        <v>48891234.43</v>
+        <v>66811704.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>21242826.68</v>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+        <v>87052155.19</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>21855965.61</v>
+      </c>
       <c r="AY5" t="n">
-        <v>3177428768.65</v>
+        <v>3073679815</v>
       </c>
       <c r="AZ5" t="n">
-        <v>2164686340</v>
+        <v>2437394079.21</v>
       </c>
       <c r="BA5" t="n">
-        <v>5342115108.65</v>
+        <v>5511073894.21</v>
       </c>
       <c r="BB5" t="n">
-        <v>5342115108.65</v>
+        <v>5511073894.21</v>
       </c>
     </row>
   </sheetData>
@@ -1719,878 +1719,878 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>849622855</v>
+        <v>849570594</v>
       </c>
       <c r="C2" t="n">
-        <v>849622855</v>
+        <v>849570594</v>
       </c>
       <c r="D2" t="n">
-        <v>1790424444.93</v>
+        <v>1525342893.56</v>
       </c>
       <c r="E2" t="n">
-        <v>10842576426.68</v>
+        <v>5793888627.54</v>
       </c>
       <c r="F2" t="n">
-        <v>14001201623.5</v>
+        <v>8662331986.91</v>
       </c>
       <c r="G2" t="n">
-        <v>9072011193.85</v>
+        <v>6191200258.79</v>
       </c>
       <c r="H2" t="n">
-        <v>10842576426.68</v>
-      </c>
-      <c r="I2" t="n">
-        <v>14405483.37</v>
-      </c>
+        <v>5793888627.54</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>12394471246.98</v>
+        <v>7243496083.31</v>
       </c>
       <c r="K2" t="n">
-        <v>14001201623.5</v>
+        <v>8612331986.91</v>
       </c>
       <c r="L2" t="n">
-        <v>12394471246.98</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
+        <v>7291883378.37</v>
+      </c>
+      <c r="M2" t="n">
+        <v>48387295.06</v>
+      </c>
       <c r="N2" t="n">
-        <v>12394471246.98</v>
+        <v>7243496083.31</v>
       </c>
       <c r="O2" t="n">
-        <v>175871556.44</v>
-      </c>
-      <c r="P2" t="n">
-        <v>600012966.11</v>
-      </c>
+        <v>176480592.4</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>10958611984.6</v>
+        <v>5444555455.56</v>
       </c>
       <c r="R2" t="n">
-        <v>372536319.94</v>
+        <v>616736696.99</v>
       </c>
       <c r="S2" t="n">
-        <v>849622855</v>
+        <v>606837179</v>
       </c>
       <c r="T2" t="n">
-        <v>849622855</v>
+        <v>606837179</v>
       </c>
       <c r="U2" t="n">
-        <v>4925291099.08</v>
+        <v>4300364965.52</v>
       </c>
       <c r="V2" t="n">
-        <v>2336825787.78</v>
-      </c>
-      <c r="W2" t="n">
-        <v>20000000</v>
-      </c>
+        <v>1661042198.33</v>
+      </c>
+      <c r="W2" t="inlineStr"/>
       <c r="X2" t="n">
-        <v>800000</v>
+        <v>28771749.42</v>
       </c>
       <c r="Y2" t="n">
-        <v>597398902.08</v>
+        <v>185648969.22</v>
       </c>
       <c r="Z2" t="n">
-        <v>97491025.81</v>
+        <v>77785576.09</v>
       </c>
       <c r="AA2" t="n">
-        <v>1621135859.89</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>14405483.37</v>
-      </c>
+        <v>1368835903.6</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>1606730376.52</v>
+        <v>1368835903.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>2588465311.3</v>
+        <v>2639322767.19</v>
       </c>
       <c r="AE2" t="n">
-        <v>50008824.42</v>
+        <v>108758909.15</v>
       </c>
       <c r="AF2" t="n">
-        <v>169288585.04</v>
-      </c>
-      <c r="AG2" t="inlineStr"/>
+        <v>156506989.96</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>50000000</v>
+      </c>
       <c r="AH2" t="n">
-        <v>2085237276.4</v>
+        <v>1903334488.41</v>
       </c>
       <c r="AI2" t="n">
-        <v>645201951.36</v>
+        <v>574162461.41</v>
       </c>
       <c r="AJ2" t="n">
-        <v>85921210.26000001</v>
+        <v>106134824.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>1354114114.78</v>
+        <v>1223037202.69</v>
       </c>
       <c r="AL2" t="n">
-        <v>17319762346.06</v>
+        <v>11592248343.89</v>
       </c>
       <c r="AM2" t="n">
-        <v>5659285840.91</v>
+        <v>2761725317.91</v>
       </c>
       <c r="AN2" t="n">
-        <v>2271868125.22</v>
+        <v>10075204.84</v>
       </c>
       <c r="AO2" t="n">
-        <v>50654877.55</v>
+        <v>24166744.62</v>
       </c>
       <c r="AP2" t="n">
-        <v>41062311.74</v>
+        <v>39760353.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>139339200</v>
+        <v>74783624.33</v>
       </c>
       <c r="AR2" t="n">
-        <v>139339200</v>
+        <v>74783624.33</v>
       </c>
       <c r="AS2" t="n">
-        <v>534749620.79</v>
+        <v>346631577.71</v>
       </c>
       <c r="AT2" t="n">
-        <v>379188042.76</v>
+        <v>460964557.58</v>
       </c>
       <c r="AU2" t="n">
-        <v>1551894820.3</v>
+        <v>1449607455.77</v>
       </c>
       <c r="AV2" t="n">
-        <v>866218803.35</v>
+        <v>763931438.8200001</v>
       </c>
       <c r="AW2" t="n">
         <v>685676016.95</v>
       </c>
       <c r="AX2" t="n">
-        <v>690528842.55</v>
+        <v>355735799.36</v>
       </c>
       <c r="AY2" t="n">
-        <v>-748773035.4</v>
+        <v>-532424607.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1439301877.95</v>
+        <v>888160406.47</v>
       </c>
       <c r="BA2" t="n">
-        <v>65064418.97</v>
+        <v>111231740.57</v>
       </c>
       <c r="BB2" t="n">
-        <v>340336039.34</v>
+        <v>194726812.37</v>
       </c>
       <c r="BC2" t="n">
-        <v>932843079.85</v>
+        <v>486733718.08</v>
       </c>
       <c r="BD2" t="n">
-        <v>101058339.79</v>
+        <v>95468135.45</v>
       </c>
       <c r="BE2" t="n">
-        <v>11660476505.15</v>
+        <v>8830523025.98</v>
       </c>
       <c r="BF2" t="n">
-        <v>715431965.4</v>
+        <v>6849784.34</v>
       </c>
       <c r="BG2" t="n">
-        <v>132916465.18</v>
+        <v>374468887.59</v>
       </c>
       <c r="BH2" t="n">
-        <v>1973721140.88</v>
+        <v>1223164636.47</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>119180235.81</v>
+        <v>127157520.07</v>
       </c>
       <c r="BK2" t="n">
-        <v>893285200.12</v>
+        <v>431791649.64</v>
       </c>
       <c r="BL2" t="n">
-        <v>349372990.02</v>
+        <v>257248695.78</v>
       </c>
       <c r="BM2" t="n">
-        <v>611882714.9299999</v>
+        <v>406966770.98</v>
       </c>
       <c r="BN2" t="n">
-        <v>1535351290.26</v>
+        <v>1691545777.56</v>
       </c>
       <c r="BO2" t="n">
-        <v>4056731829.3</v>
+        <v>2371982196.74</v>
       </c>
       <c r="BP2" t="n">
-        <v>-117905633.85</v>
+        <v>-44566962.14</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4174637463.15</v>
+        <v>2416549158.88</v>
       </c>
       <c r="BR2" t="n">
-        <v>3246323814.13</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>785209035.61</v>
-      </c>
+        <v>3162511743.28</v>
+      </c>
+      <c r="BS2" t="inlineStr"/>
       <c r="BT2" t="n">
-        <v>2461114778.52</v>
+        <v>3162511743.28</v>
       </c>
       <c r="BU2" t="n">
-        <v>94193174.31</v>
+        <v>194388191.59</v>
       </c>
       <c r="BV2" t="n">
-        <v>2366921604.21</v>
+        <v>2968123551.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>849619317</v>
+        <v>849608551</v>
       </c>
       <c r="C3" t="n">
-        <v>849619317</v>
+        <v>849608551</v>
       </c>
       <c r="D3" t="n">
-        <v>1966013726.58</v>
+        <v>1842722660.61</v>
       </c>
       <c r="E3" t="n">
-        <v>10082876004.09</v>
+        <v>8636350907.639999</v>
       </c>
       <c r="F3" t="n">
-        <v>13206325470.23</v>
+        <v>11463647528.07</v>
       </c>
       <c r="G3" t="n">
-        <v>10155829441.58</v>
+        <v>8776984585.82</v>
       </c>
       <c r="H3" t="n">
-        <v>10082876004.09</v>
+        <v>8636350907.639999</v>
       </c>
       <c r="I3" t="n">
-        <v>30798249.43</v>
+        <v>11697186.98</v>
       </c>
       <c r="J3" t="n">
-        <v>11656820452.74</v>
+        <v>9703075490.59</v>
       </c>
       <c r="K3" t="n">
-        <v>13168393261.61</v>
+        <v>11463647528.07</v>
       </c>
       <c r="L3" t="n">
-        <v>11730620425.84</v>
+        <v>9775154662.34</v>
       </c>
       <c r="M3" t="n">
-        <v>73799973.09999999</v>
+        <v>72079171.75</v>
       </c>
       <c r="N3" t="n">
-        <v>11656820452.74</v>
+        <v>9703075490.59</v>
       </c>
       <c r="O3" t="n">
-        <v>175912455.06</v>
-      </c>
-      <c r="P3" t="n">
-        <v>600012966.11</v>
-      </c>
+        <v>176037873.59</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>10364707670.88</v>
+        <v>7876395826.87</v>
       </c>
       <c r="R3" t="n">
-        <v>378719517.46</v>
+        <v>377744145.96</v>
       </c>
       <c r="S3" t="n">
-        <v>849619317</v>
+        <v>849608551</v>
       </c>
       <c r="T3" t="n">
-        <v>849619317</v>
+        <v>849608551</v>
       </c>
       <c r="U3" t="n">
-        <v>6335029972.54</v>
+        <v>5553599463.48</v>
       </c>
       <c r="V3" t="n">
-        <v>2402564917.48</v>
+        <v>2076145115.13</v>
       </c>
       <c r="W3" t="n">
-        <v>115000000</v>
+        <v>175000000</v>
       </c>
       <c r="X3" t="n">
         <v>800000</v>
       </c>
       <c r="Y3" t="n">
-        <v>654559230.99</v>
+        <v>54090066.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>89834628.19</v>
+        <v>73985824.37</v>
       </c>
       <c r="AA3" t="n">
-        <v>1542371058.3</v>
+        <v>1772269224.46</v>
       </c>
       <c r="AB3" t="n">
-        <v>30798249.43</v>
+        <v>11697186.98</v>
       </c>
       <c r="AC3" t="n">
-        <v>1511572808.87</v>
+        <v>1760572037.48</v>
       </c>
       <c r="AD3" t="n">
-        <v>3932465055.06</v>
+        <v>3477454348.35</v>
       </c>
       <c r="AE3" t="n">
-        <v>186329789.35</v>
+        <v>331680306.89</v>
       </c>
       <c r="AF3" t="n">
-        <v>423642668.28</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>37932208.62</v>
-      </c>
+        <v>70453436.15000001</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>2552964206.97</v>
+        <v>2272695601.66</v>
       </c>
       <c r="AI3" t="n">
-        <v>897527116.47</v>
+        <v>826052925.76</v>
       </c>
       <c r="AJ3" t="n">
-        <v>219279451.11</v>
+        <v>92278589.68000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>1436157639.39</v>
+        <v>1354364086.22</v>
       </c>
       <c r="AL3" t="n">
-        <v>18065650398.38</v>
+        <v>15328754125.82</v>
       </c>
       <c r="AM3" t="n">
-        <v>3977355901.74</v>
+        <v>3074315191.65</v>
       </c>
       <c r="AN3" t="n">
-        <v>698232938.5</v>
+        <v>591789953.38</v>
       </c>
       <c r="AO3" t="n">
-        <v>42198988.02</v>
+        <v>33442587.79</v>
       </c>
       <c r="AP3" t="n">
-        <v>56393780.65</v>
+        <v>19616509.24</v>
       </c>
       <c r="AQ3" t="n">
-        <v>78934802.12</v>
+        <v>64703624.33</v>
       </c>
       <c r="AR3" t="n">
-        <v>78934802.12</v>
+        <v>64703624.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>504826637.87</v>
+        <v>447336678.26</v>
       </c>
       <c r="AT3" t="n">
-        <v>392858572.76</v>
+        <v>402316892.24</v>
       </c>
       <c r="AU3" t="n">
-        <v>1573944448.65</v>
+        <v>1066724582.95</v>
       </c>
       <c r="AV3" t="n">
-        <v>888268431.7</v>
+        <v>381048566</v>
       </c>
       <c r="AW3" t="n">
         <v>685676016.95</v>
       </c>
       <c r="AX3" t="n">
-        <v>629965733.17</v>
+        <v>448384363.46</v>
       </c>
       <c r="AY3" t="n">
-        <v>-589146304.1900001</v>
+        <v>-562505258.03</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1219112037.36</v>
+        <v>1010889621.49</v>
       </c>
       <c r="BA3" t="n">
-        <v>33159096.83</v>
+        <v>47392311.96</v>
       </c>
       <c r="BB3" t="n">
-        <v>317606145.05</v>
+        <v>245113483.78</v>
       </c>
       <c r="BC3" t="n">
-        <v>767288455.6900001</v>
+        <v>621034660.27</v>
       </c>
       <c r="BD3" t="n">
-        <v>101058339.79</v>
+        <v>97349165.48</v>
       </c>
       <c r="BE3" t="n">
-        <v>14088294496.64</v>
+        <v>12254438934.17</v>
       </c>
       <c r="BF3" t="n">
-        <v>926538005.04</v>
+        <v>43557829.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>248034136.37</v>
+        <v>436342561.04</v>
       </c>
       <c r="BH3" t="n">
-        <v>2513444540.74</v>
+        <v>2213238094.35</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>134266174.83</v>
+        <v>107600267.34</v>
       </c>
       <c r="BK3" t="n">
-        <v>1178441396.23</v>
+        <v>1009931008.48</v>
       </c>
       <c r="BL3" t="n">
-        <v>490542100.95</v>
+        <v>482883354.47</v>
       </c>
       <c r="BM3" t="n">
-        <v>710194868.73</v>
+        <v>612823464.0599999</v>
       </c>
       <c r="BN3" t="n">
-        <v>1952893453.51</v>
+        <v>2363420203.03</v>
       </c>
       <c r="BO3" t="n">
-        <v>4308083936.87</v>
+        <v>3105706684.84</v>
       </c>
       <c r="BP3" t="n">
-        <v>-35254068.86</v>
+        <v>-26595593.9</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4361927081.93</v>
+        <v>3132302278.74</v>
       </c>
       <c r="BR3" t="n">
-        <v>4139300424.11</v>
-      </c>
-      <c r="BS3" t="n">
-        <v>1041584071.23</v>
-      </c>
+        <v>4092173560.99</v>
+      </c>
+      <c r="BS3" t="inlineStr"/>
       <c r="BT3" t="n">
-        <v>3097716352.88</v>
+        <v>4092173560.99</v>
       </c>
       <c r="BU3" t="n">
-        <v>79424684.87</v>
+        <v>315852282.33</v>
       </c>
       <c r="BV3" t="n">
-        <v>3002648566.73</v>
+        <v>3776321278.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>849608551</v>
+        <v>849619317</v>
       </c>
       <c r="C4" t="n">
-        <v>849608551</v>
+        <v>849619317</v>
       </c>
       <c r="D4" t="n">
-        <v>1842722660.61</v>
+        <v>1966013726.58</v>
       </c>
       <c r="E4" t="n">
-        <v>8636350907.639999</v>
+        <v>10082876004.09</v>
       </c>
       <c r="F4" t="n">
-        <v>11463647528.07</v>
+        <v>13206325470.23</v>
       </c>
       <c r="G4" t="n">
-        <v>8776984585.82</v>
+        <v>10155829441.58</v>
       </c>
       <c r="H4" t="n">
-        <v>8636350907.639999</v>
+        <v>10082876004.09</v>
       </c>
       <c r="I4" t="n">
-        <v>11697186.98</v>
+        <v>30798249.43</v>
       </c>
       <c r="J4" t="n">
-        <v>9703075490.59</v>
+        <v>11656820452.74</v>
       </c>
       <c r="K4" t="n">
-        <v>11463647528.07</v>
+        <v>13168393261.61</v>
       </c>
       <c r="L4" t="n">
-        <v>9775154662.34</v>
+        <v>11730620425.84</v>
       </c>
       <c r="M4" t="n">
-        <v>72079171.75</v>
+        <v>73799973.09999999</v>
       </c>
       <c r="N4" t="n">
-        <v>9703075490.59</v>
+        <v>11656820452.74</v>
       </c>
       <c r="O4" t="n">
-        <v>176037873.59</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>175912455.06</v>
+      </c>
+      <c r="P4" t="n">
+        <v>600012966.11</v>
+      </c>
       <c r="Q4" t="n">
-        <v>7876395826.87</v>
+        <v>10364707670.88</v>
       </c>
       <c r="R4" t="n">
-        <v>377744145.96</v>
+        <v>378719517.46</v>
       </c>
       <c r="S4" t="n">
-        <v>849608551</v>
+        <v>849619317</v>
       </c>
       <c r="T4" t="n">
-        <v>849608551</v>
+        <v>849619317</v>
       </c>
       <c r="U4" t="n">
-        <v>5553599463.48</v>
+        <v>6335029972.54</v>
       </c>
       <c r="V4" t="n">
-        <v>2076145115.13</v>
+        <v>2402564917.48</v>
       </c>
       <c r="W4" t="n">
-        <v>175000000</v>
+        <v>115000000</v>
       </c>
       <c r="X4" t="n">
         <v>800000</v>
       </c>
       <c r="Y4" t="n">
-        <v>54090066.3</v>
+        <v>654559230.99</v>
       </c>
       <c r="Z4" t="n">
-        <v>73985824.37</v>
+        <v>89834628.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>1772269224.46</v>
+        <v>1542371058.3</v>
       </c>
       <c r="AB4" t="n">
-        <v>11697186.98</v>
+        <v>30798249.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>1760572037.48</v>
+        <v>1511572808.87</v>
       </c>
       <c r="AD4" t="n">
-        <v>3477454348.35</v>
+        <v>3932465055.06</v>
       </c>
       <c r="AE4" t="n">
-        <v>331680306.89</v>
+        <v>186329789.35</v>
       </c>
       <c r="AF4" t="n">
-        <v>70453436.15000001</v>
-      </c>
-      <c r="AG4" t="inlineStr"/>
+        <v>423642668.28</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>37932208.62</v>
+      </c>
       <c r="AH4" t="n">
-        <v>2272695601.66</v>
+        <v>2552964206.97</v>
       </c>
       <c r="AI4" t="n">
-        <v>826052925.76</v>
+        <v>897527116.47</v>
       </c>
       <c r="AJ4" t="n">
-        <v>92278589.68000001</v>
+        <v>219279451.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1354364086.22</v>
+        <v>1436157639.39</v>
       </c>
       <c r="AL4" t="n">
-        <v>15328754125.82</v>
+        <v>18065650398.38</v>
       </c>
       <c r="AM4" t="n">
-        <v>3074315191.65</v>
+        <v>3977355901.74</v>
       </c>
       <c r="AN4" t="n">
-        <v>591789953.38</v>
+        <v>698232938.5</v>
       </c>
       <c r="AO4" t="n">
-        <v>33442587.79</v>
+        <v>42198988.02</v>
       </c>
       <c r="AP4" t="n">
-        <v>19616509.24</v>
+        <v>56393780.65</v>
       </c>
       <c r="AQ4" t="n">
-        <v>64703624.33</v>
+        <v>78934802.12</v>
       </c>
       <c r="AR4" t="n">
-        <v>64703624.33</v>
+        <v>78934802.12</v>
       </c>
       <c r="AS4" t="n">
-        <v>447336678.26</v>
+        <v>504826637.87</v>
       </c>
       <c r="AT4" t="n">
-        <v>402316892.24</v>
+        <v>392858572.76</v>
       </c>
       <c r="AU4" t="n">
-        <v>1066724582.95</v>
+        <v>1573944448.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>381048566</v>
+        <v>888268431.7</v>
       </c>
       <c r="AW4" t="n">
         <v>685676016.95</v>
       </c>
       <c r="AX4" t="n">
-        <v>448384363.46</v>
+        <v>629965733.17</v>
       </c>
       <c r="AY4" t="n">
-        <v>-562505258.03</v>
+        <v>-589146304.1900001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1010889621.49</v>
+        <v>1219112037.36</v>
       </c>
       <c r="BA4" t="n">
-        <v>47392311.96</v>
+        <v>33159096.83</v>
       </c>
       <c r="BB4" t="n">
-        <v>245113483.78</v>
+        <v>317606145.05</v>
       </c>
       <c r="BC4" t="n">
-        <v>621034660.27</v>
+        <v>767288455.6900001</v>
       </c>
       <c r="BD4" t="n">
-        <v>97349165.48</v>
+        <v>101058339.79</v>
       </c>
       <c r="BE4" t="n">
-        <v>12254438934.17</v>
+        <v>14088294496.64</v>
       </c>
       <c r="BF4" t="n">
-        <v>43557829.92</v>
+        <v>926538005.04</v>
       </c>
       <c r="BG4" t="n">
-        <v>436342561.04</v>
+        <v>248034136.37</v>
       </c>
       <c r="BH4" t="n">
-        <v>2213238094.35</v>
+        <v>2513444540.74</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>107600267.34</v>
+        <v>134266174.83</v>
       </c>
       <c r="BK4" t="n">
-        <v>1009931008.48</v>
+        <v>1178441396.23</v>
       </c>
       <c r="BL4" t="n">
-        <v>482883354.47</v>
+        <v>490542100.95</v>
       </c>
       <c r="BM4" t="n">
-        <v>612823464.0599999</v>
+        <v>710194868.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>2363420203.03</v>
+        <v>1952893453.51</v>
       </c>
       <c r="BO4" t="n">
-        <v>3105706684.84</v>
+        <v>4308083936.87</v>
       </c>
       <c r="BP4" t="n">
-        <v>-26595593.9</v>
+        <v>-35254068.86</v>
       </c>
       <c r="BQ4" t="n">
-        <v>3132302278.74</v>
+        <v>4361927081.93</v>
       </c>
       <c r="BR4" t="n">
-        <v>4092173560.99</v>
-      </c>
-      <c r="BS4" t="inlineStr"/>
+        <v>4139300424.11</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1041584071.23</v>
+      </c>
       <c r="BT4" t="n">
-        <v>4092173560.99</v>
+        <v>3097716352.88</v>
       </c>
       <c r="BU4" t="n">
-        <v>315852282.33</v>
+        <v>79424684.87</v>
       </c>
       <c r="BV4" t="n">
-        <v>3776321278.66</v>
+        <v>3002648566.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>849570594</v>
+        <v>849622855</v>
       </c>
       <c r="C5" t="n">
-        <v>849570594</v>
+        <v>849622855</v>
       </c>
       <c r="D5" t="n">
-        <v>1525342893.56</v>
+        <v>1790424444.93</v>
       </c>
       <c r="E5" t="n">
-        <v>5793888627.54</v>
+        <v>10842576426.68</v>
       </c>
       <c r="F5" t="n">
-        <v>8662331986.91</v>
+        <v>14001201623.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6191200258.79</v>
+        <v>9072011193.85</v>
       </c>
       <c r="H5" t="n">
-        <v>5793888627.54</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>10842576426.68</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14405483.37</v>
+      </c>
       <c r="J5" t="n">
-        <v>7243496083.31</v>
+        <v>12394471246.98</v>
       </c>
       <c r="K5" t="n">
-        <v>8612331986.91</v>
+        <v>14001201623.5</v>
       </c>
       <c r="L5" t="n">
-        <v>7291883378.37</v>
-      </c>
-      <c r="M5" t="n">
-        <v>48387295.06</v>
-      </c>
+        <v>12394471246.98</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
-        <v>7243496083.31</v>
+        <v>12394471246.98</v>
       </c>
       <c r="O5" t="n">
-        <v>176480592.4</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>175871556.44</v>
+      </c>
+      <c r="P5" t="n">
+        <v>600012966.11</v>
+      </c>
       <c r="Q5" t="n">
-        <v>5444555455.56</v>
+        <v>10958611984.6</v>
       </c>
       <c r="R5" t="n">
-        <v>616736696.99</v>
+        <v>372536319.94</v>
       </c>
       <c r="S5" t="n">
-        <v>606837179</v>
+        <v>849622855</v>
       </c>
       <c r="T5" t="n">
-        <v>606837179</v>
+        <v>849622855</v>
       </c>
       <c r="U5" t="n">
-        <v>4300364965.52</v>
+        <v>4925291099.08</v>
       </c>
       <c r="V5" t="n">
-        <v>1661042198.33</v>
-      </c>
-      <c r="W5" t="inlineStr"/>
+        <v>2336825787.78</v>
+      </c>
+      <c r="W5" t="n">
+        <v>20000000</v>
+      </c>
       <c r="X5" t="n">
-        <v>28771749.42</v>
+        <v>800000</v>
       </c>
       <c r="Y5" t="n">
-        <v>185648969.22</v>
+        <v>597398902.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>77785576.09</v>
+        <v>97491025.81</v>
       </c>
       <c r="AA5" t="n">
-        <v>1368835903.6</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>1621135859.89</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>14405483.37</v>
+      </c>
       <c r="AC5" t="n">
-        <v>1368835903.6</v>
+        <v>1606730376.52</v>
       </c>
       <c r="AD5" t="n">
-        <v>2639322767.19</v>
+        <v>2588465311.3</v>
       </c>
       <c r="AE5" t="n">
-        <v>108758909.15</v>
+        <v>50008824.42</v>
       </c>
       <c r="AF5" t="n">
-        <v>156506989.96</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>50000000</v>
-      </c>
+        <v>169288585.04</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="n">
-        <v>1903334488.41</v>
+        <v>2085237276.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>574162461.41</v>
+        <v>645201951.36</v>
       </c>
       <c r="AJ5" t="n">
-        <v>106134824.31</v>
+        <v>85921210.26000001</v>
       </c>
       <c r="AK5" t="n">
-        <v>1223037202.69</v>
+        <v>1354114114.78</v>
       </c>
       <c r="AL5" t="n">
-        <v>11592248343.89</v>
+        <v>17319762346.06</v>
       </c>
       <c r="AM5" t="n">
-        <v>2761725317.91</v>
+        <v>5659285840.91</v>
       </c>
       <c r="AN5" t="n">
-        <v>10075204.84</v>
+        <v>2271868125.22</v>
       </c>
       <c r="AO5" t="n">
-        <v>24166744.62</v>
+        <v>50654877.55</v>
       </c>
       <c r="AP5" t="n">
-        <v>39760353.7</v>
+        <v>41062311.74</v>
       </c>
       <c r="AQ5" t="n">
-        <v>74783624.33</v>
+        <v>139339200</v>
       </c>
       <c r="AR5" t="n">
-        <v>74783624.33</v>
+        <v>139339200</v>
       </c>
       <c r="AS5" t="n">
-        <v>346631577.71</v>
+        <v>534749620.79</v>
       </c>
       <c r="AT5" t="n">
-        <v>460964557.58</v>
+        <v>379188042.76</v>
       </c>
       <c r="AU5" t="n">
-        <v>1449607455.77</v>
+        <v>1551894820.3</v>
       </c>
       <c r="AV5" t="n">
-        <v>763931438.8200001</v>
+        <v>866218803.35</v>
       </c>
       <c r="AW5" t="n">
         <v>685676016.95</v>
       </c>
       <c r="AX5" t="n">
-        <v>355735799.36</v>
+        <v>690528842.55</v>
       </c>
       <c r="AY5" t="n">
-        <v>-532424607.11</v>
+        <v>-748773035.4</v>
       </c>
       <c r="AZ5" t="n">
-        <v>888160406.47</v>
+        <v>1439301877.95</v>
       </c>
       <c r="BA5" t="n">
-        <v>111231740.57</v>
+        <v>65064418.97</v>
       </c>
       <c r="BB5" t="n">
-        <v>194726812.37</v>
+        <v>340336039.34</v>
       </c>
       <c r="BC5" t="n">
-        <v>486733718.08</v>
+        <v>932843079.85</v>
       </c>
       <c r="BD5" t="n">
-        <v>95468135.45</v>
+        <v>101058339.79</v>
       </c>
       <c r="BE5" t="n">
-        <v>8830523025.98</v>
+        <v>11660476505.15</v>
       </c>
       <c r="BF5" t="n">
-        <v>6849784.34</v>
+        <v>715431965.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>374468887.59</v>
+        <v>132916465.18</v>
       </c>
       <c r="BH5" t="n">
-        <v>1223164636.47</v>
+        <v>1973721140.88</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>127157520.07</v>
+        <v>119180235.81</v>
       </c>
       <c r="BK5" t="n">
-        <v>431791649.64</v>
+        <v>893285200.12</v>
       </c>
       <c r="BL5" t="n">
-        <v>257248695.78</v>
+        <v>349372990.02</v>
       </c>
       <c r="BM5" t="n">
-        <v>406966770.98</v>
+        <v>611882714.9299999</v>
       </c>
       <c r="BN5" t="n">
-        <v>1691545777.56</v>
+        <v>1535351290.26</v>
       </c>
       <c r="BO5" t="n">
-        <v>2371982196.74</v>
+        <v>4056731829.3</v>
       </c>
       <c r="BP5" t="n">
-        <v>-44566962.14</v>
+        <v>-117905633.85</v>
       </c>
       <c r="BQ5" t="n">
-        <v>2416549158.88</v>
+        <v>4174637463.15</v>
       </c>
       <c r="BR5" t="n">
-        <v>3162511743.28</v>
-      </c>
-      <c r="BS5" t="inlineStr"/>
+        <v>3246323814.13</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>785209035.61</v>
+      </c>
       <c r="BT5" t="n">
-        <v>3162511743.28</v>
+        <v>2461114778.52</v>
       </c>
       <c r="BU5" t="n">
-        <v>194388191.59</v>
+        <v>94193174.31</v>
       </c>
       <c r="BV5" t="n">
-        <v>2968123551.69</v>
+        <v>2366921604.21</v>
       </c>
     </row>
   </sheetData>
@@ -2841,566 +2841,566 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1150791164.18</v>
+        <v>768931991.96</v>
       </c>
       <c r="C2" t="n">
-        <v>-372490063.01</v>
+        <v>-767496812.4400001</v>
       </c>
       <c r="D2" t="n">
-        <v>157891247.07</v>
+        <v>208635019.66</v>
       </c>
       <c r="E2" t="n">
-        <v>-316587887.26</v>
+        <v>-423580806.03</v>
       </c>
       <c r="F2" t="n">
-        <v>2364932809.24</v>
+        <v>2968123551.69</v>
       </c>
       <c r="G2" t="n">
-        <v>3016302852.88</v>
+        <v>1236065120.63</v>
       </c>
       <c r="H2" t="n">
-        <v>7443168.72</v>
+        <v>-1914524.69</v>
       </c>
       <c r="I2" t="n">
-        <v>-658813212.36</v>
+        <v>1733972955.75</v>
       </c>
       <c r="J2" t="n">
-        <v>-859321762.75</v>
+        <v>932578292.1</v>
       </c>
       <c r="K2" t="n">
-        <v>-54448311.09</v>
+        <v>1606378956.72</v>
       </c>
       <c r="L2" t="n">
-        <v>-590274635.72</v>
+        <v>-114938871.84</v>
       </c>
       <c r="M2" t="n">
-        <v>-214598815.94</v>
+        <v>-558861792.78</v>
       </c>
       <c r="N2" t="n">
-        <v>-214598815.94</v>
+        <v>-558861792.78</v>
       </c>
       <c r="O2" t="n">
-        <v>-372490063.01</v>
+        <v>-767496812.4400001</v>
       </c>
       <c r="P2" t="n">
-        <v>157891247.07</v>
+        <v>208635019.66</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1266870501.05</v>
+        <v>-391118134.34</v>
       </c>
       <c r="R2" t="n">
-        <v>-1063079945.8</v>
+        <v>-1062757.21</v>
       </c>
       <c r="S2" t="n">
-        <v>59004716.61</v>
+        <v>24776335</v>
       </c>
       <c r="T2" t="n">
-        <v>59004716.61</v>
-      </c>
-      <c r="U2" t="n">
-        <v>52984227.83</v>
-      </c>
-      <c r="V2" t="n">
-        <v>52984227.83</v>
-      </c>
+        <v>24776335</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>-315779499.69</v>
+        <v>-414831712.13</v>
       </c>
       <c r="X2" t="n">
-        <v>808387.5699999999</v>
+        <v>8749093.9</v>
       </c>
       <c r="Y2" t="n">
-        <v>-316587887.26</v>
+        <v>-423580806.03</v>
       </c>
       <c r="Z2" t="n">
-        <v>1467379051.44</v>
+        <v>1192512797.99</v>
       </c>
       <c r="AA2" t="n">
-        <v>-90360545.59999999</v>
+        <v>-952713015.46</v>
       </c>
       <c r="AB2" t="n">
-        <v>23016159.43</v>
+        <v>-10897067.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>-984041077.35</v>
+        <v>912132030.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>361526633.97</v>
+        <v>-330946200.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>509137738.35</v>
+        <v>-1523001778.64</v>
       </c>
       <c r="AF2" t="n">
-        <v>27917705.12</v>
+        <v>62879146.12</v>
       </c>
       <c r="AG2" t="n">
-        <v>234926567.64</v>
+        <v>175328031.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>78024842.54000001</v>
+        <v>130607647.32</v>
       </c>
       <c r="AI2" t="n">
-        <v>156901725.1</v>
+        <v>44720384.32</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-39174036.16</v>
+        <v>-80003701.62</v>
       </c>
       <c r="AK2" t="n">
-        <v>-324684.49</v>
+        <v>-3656078.81</v>
       </c>
       <c r="AL2" t="n">
-        <v>1185418098.61</v>
+        <v>1983992310.11</v>
       </c>
       <c r="AM2" t="n">
-        <v>1467379051.44</v>
+        <v>1192512797.99</v>
       </c>
       <c r="AN2" t="n">
-        <v>-462047695.38</v>
+        <v>-474563335.57</v>
       </c>
       <c r="AO2" t="n">
-        <v>-3978902746.19</v>
+        <v>-3201966417.79</v>
       </c>
       <c r="AP2" t="n">
-        <v>-680253005.49</v>
+        <v>-341404649.42</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-1504477178.46</v>
+        <v>-670868619.01</v>
       </c>
       <c r="AR2" t="n">
-        <v>-1794172562.24</v>
+        <v>-2189693149.36</v>
       </c>
       <c r="AS2" t="n">
-        <v>5908329493.01</v>
+        <v>4869042551.35</v>
       </c>
       <c r="AT2" t="n">
-        <v>280362656.6</v>
+        <v>198331280.73</v>
       </c>
       <c r="AU2" t="n">
-        <v>5627966836.41</v>
+        <v>4670711270.62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1518218101.12</v>
+        <v>1419195157.36</v>
       </c>
       <c r="C3" t="n">
-        <v>-60504700</v>
+        <v>-262449242.36</v>
       </c>
       <c r="D3" t="n">
-        <v>37900000</v>
+        <v>536000000</v>
       </c>
       <c r="E3" t="n">
-        <v>-251231092.82</v>
+        <v>-307305508.3</v>
       </c>
       <c r="F3" t="n">
-        <v>3016302852.88</v>
+        <v>3776321278.66</v>
       </c>
       <c r="G3" t="n">
-        <v>3796323246.86</v>
+        <v>2968123551.69</v>
       </c>
       <c r="H3" t="n">
-        <v>10971413.3</v>
+        <v>19878599.81</v>
       </c>
       <c r="I3" t="n">
-        <v>-790991807.28</v>
+        <v>788319127.16</v>
       </c>
       <c r="J3" t="n">
-        <v>-261599676.43</v>
+        <v>-105010243.68</v>
       </c>
       <c r="K3" t="n">
-        <v>-219713178.66</v>
+        <v>-163497843.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-19281797.77</v>
+        <v>-215063158.22</v>
       </c>
       <c r="M3" t="n">
-        <v>-22604700</v>
+        <v>273550757.64</v>
       </c>
       <c r="N3" t="n">
-        <v>-22604700</v>
+        <v>273550757.64</v>
       </c>
       <c r="O3" t="n">
-        <v>-60504700</v>
+        <v>-262449242.36</v>
       </c>
       <c r="P3" t="n">
-        <v>37900000</v>
+        <v>536000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2298841324.79</v>
+        <v>-833171294.8200001</v>
       </c>
       <c r="R3" t="n">
-        <v>-2077113763.74</v>
+        <v>-530001968.2</v>
       </c>
       <c r="S3" t="n">
-        <v>12962606.87</v>
+        <v>2902450.68</v>
       </c>
       <c r="T3" t="n">
-        <v>12962606.87</v>
-      </c>
-      <c r="U3" t="n">
-        <v>16032163.9</v>
-      </c>
-      <c r="V3" t="n">
-        <v>16032163.9</v>
-      </c>
+        <v>2902450.68</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>-250722331.82</v>
+        <v>-306071777.3</v>
       </c>
       <c r="X3" t="n">
-        <v>508761</v>
+        <v>1233731</v>
       </c>
       <c r="Y3" t="n">
-        <v>-251231092.82</v>
+        <v>-307305508.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>1769449193.94</v>
+        <v>1726500665.66</v>
       </c>
       <c r="AA3" t="n">
-        <v>-1020127241.43</v>
+        <v>-1250739638.04</v>
       </c>
       <c r="AB3" t="n">
-        <v>-20899645.37</v>
+        <v>16478723.19</v>
       </c>
       <c r="AC3" t="n">
-        <v>275464395.19</v>
+        <v>1006783947.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>-365308798.93</v>
+        <v>-1045972733.85</v>
       </c>
       <c r="AE3" t="n">
-        <v>-909383192.3200001</v>
+        <v>-1228029575.08</v>
       </c>
       <c r="AF3" t="n">
-        <v>48107718.68</v>
+        <v>59703217.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>223109950.76</v>
+        <v>305603531.03</v>
       </c>
       <c r="AH3" t="n">
-        <v>101638853.02</v>
+        <v>236279323.59</v>
       </c>
       <c r="AI3" t="n">
-        <v>121471097.74</v>
+        <v>69324207.44</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-88151952.93000001</v>
+        <v>-71044939.54000001</v>
       </c>
       <c r="AK3" t="n">
-        <v>-118572.84</v>
+        <v>-550405.52</v>
       </c>
       <c r="AL3" t="n">
-        <v>2534626412.72</v>
+        <v>2640412086.12</v>
       </c>
       <c r="AM3" t="n">
-        <v>1769449193.94</v>
+        <v>1726500665.66</v>
       </c>
       <c r="AN3" t="n">
-        <v>-592794654.13</v>
+        <v>-732783931.99</v>
       </c>
       <c r="AO3" t="n">
-        <v>-4803938965.13</v>
+        <v>-4608377984.99</v>
       </c>
       <c r="AP3" t="n">
-        <v>-507817969.31</v>
+        <v>-404348900.63</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-1449034895.35</v>
+        <v>-1122327621.21</v>
       </c>
       <c r="AR3" t="n">
-        <v>-2847086100.47</v>
+        <v>-3081701463.15</v>
       </c>
       <c r="AS3" t="n">
-        <v>7166182813.2</v>
+        <v>7067662582.64</v>
       </c>
       <c r="AT3" t="n">
-        <v>360278473.84</v>
+        <v>575981027.52</v>
       </c>
       <c r="AU3" t="n">
-        <v>6805904339.36</v>
+        <v>6491681555.12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1419195157.36</v>
+        <v>1518218101.12</v>
       </c>
       <c r="C4" t="n">
-        <v>-262449242.36</v>
+        <v>-60504700</v>
       </c>
       <c r="D4" t="n">
-        <v>536000000</v>
+        <v>37900000</v>
       </c>
       <c r="E4" t="n">
-        <v>-307305508.3</v>
+        <v>-251231092.82</v>
       </c>
       <c r="F4" t="n">
-        <v>3776321278.66</v>
+        <v>3016302852.88</v>
       </c>
       <c r="G4" t="n">
-        <v>2968123551.69</v>
+        <v>3796323246.86</v>
       </c>
       <c r="H4" t="n">
-        <v>19878599.81</v>
+        <v>10971413.3</v>
       </c>
       <c r="I4" t="n">
-        <v>788319127.16</v>
+        <v>-790991807.28</v>
       </c>
       <c r="J4" t="n">
-        <v>-105010243.68</v>
+        <v>-261599676.43</v>
       </c>
       <c r="K4" t="n">
-        <v>-163497843.1</v>
+        <v>-219713178.66</v>
       </c>
       <c r="L4" t="n">
-        <v>-215063158.22</v>
+        <v>-19281797.77</v>
       </c>
       <c r="M4" t="n">
-        <v>273550757.64</v>
+        <v>-22604700</v>
       </c>
       <c r="N4" t="n">
-        <v>273550757.64</v>
+        <v>-22604700</v>
       </c>
       <c r="O4" t="n">
-        <v>-262449242.36</v>
+        <v>-60504700</v>
       </c>
       <c r="P4" t="n">
-        <v>536000000</v>
+        <v>37900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-833171294.8200001</v>
+        <v>-2298841324.79</v>
       </c>
       <c r="R4" t="n">
-        <v>-530001968.2</v>
+        <v>-2077113763.74</v>
       </c>
       <c r="S4" t="n">
-        <v>2902450.68</v>
+        <v>12962606.87</v>
       </c>
       <c r="T4" t="n">
-        <v>2902450.68</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
+        <v>12962606.87</v>
+      </c>
+      <c r="U4" t="n">
+        <v>16032163.9</v>
+      </c>
+      <c r="V4" t="n">
+        <v>16032163.9</v>
+      </c>
       <c r="W4" t="n">
-        <v>-306071777.3</v>
+        <v>-250722331.82</v>
       </c>
       <c r="X4" t="n">
-        <v>1233731</v>
+        <v>508761</v>
       </c>
       <c r="Y4" t="n">
-        <v>-307305508.3</v>
+        <v>-251231092.82</v>
       </c>
       <c r="Z4" t="n">
-        <v>1726500665.66</v>
+        <v>1769449193.94</v>
       </c>
       <c r="AA4" t="n">
-        <v>-1250739638.04</v>
+        <v>-1020127241.43</v>
       </c>
       <c r="AB4" t="n">
-        <v>16478723.19</v>
+        <v>-20899645.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>1006783947.7</v>
+        <v>275464395.19</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1045972733.85</v>
+        <v>-365308798.93</v>
       </c>
       <c r="AE4" t="n">
-        <v>-1228029575.08</v>
+        <v>-909383192.3200001</v>
       </c>
       <c r="AF4" t="n">
-        <v>59703217.17</v>
+        <v>48107718.68</v>
       </c>
       <c r="AG4" t="n">
-        <v>305603531.03</v>
+        <v>223109950.76</v>
       </c>
       <c r="AH4" t="n">
-        <v>236279323.59</v>
+        <v>101638853.02</v>
       </c>
       <c r="AI4" t="n">
-        <v>69324207.44</v>
+        <v>121471097.74</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-71044939.54000001</v>
+        <v>-88151952.93000001</v>
       </c>
       <c r="AK4" t="n">
-        <v>-550405.52</v>
+        <v>-118572.84</v>
       </c>
       <c r="AL4" t="n">
-        <v>2640412086.12</v>
+        <v>2534626412.72</v>
       </c>
       <c r="AM4" t="n">
-        <v>1726500665.66</v>
+        <v>1769449193.94</v>
       </c>
       <c r="AN4" t="n">
-        <v>-732783931.99</v>
+        <v>-592794654.13</v>
       </c>
       <c r="AO4" t="n">
-        <v>-4608377984.99</v>
+        <v>-4803938965.13</v>
       </c>
       <c r="AP4" t="n">
-        <v>-404348900.63</v>
+        <v>-507817969.31</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-1122327621.21</v>
+        <v>-1449034895.35</v>
       </c>
       <c r="AR4" t="n">
-        <v>-3081701463.15</v>
+        <v>-2847086100.47</v>
       </c>
       <c r="AS4" t="n">
-        <v>7067662582.64</v>
+        <v>7166182813.2</v>
       </c>
       <c r="AT4" t="n">
-        <v>575981027.52</v>
+        <v>360278473.84</v>
       </c>
       <c r="AU4" t="n">
-        <v>6491681555.12</v>
+        <v>6805904339.36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>768931991.96</v>
+        <v>1150791164.18</v>
       </c>
       <c r="C5" t="n">
-        <v>-767496812.4400001</v>
+        <v>-372490063.01</v>
       </c>
       <c r="D5" t="n">
-        <v>208635019.66</v>
+        <v>157891247.07</v>
       </c>
       <c r="E5" t="n">
-        <v>-423580806.03</v>
+        <v>-316587887.26</v>
       </c>
       <c r="F5" t="n">
-        <v>2968123551.69</v>
+        <v>2364932809.24</v>
       </c>
       <c r="G5" t="n">
-        <v>1236065120.63</v>
+        <v>3016302852.88</v>
       </c>
       <c r="H5" t="n">
-        <v>-1914524.69</v>
+        <v>7443168.72</v>
       </c>
       <c r="I5" t="n">
-        <v>1733972955.75</v>
+        <v>-658813212.36</v>
       </c>
       <c r="J5" t="n">
-        <v>932578292.1</v>
+        <v>-859321762.75</v>
       </c>
       <c r="K5" t="n">
-        <v>1606378956.72</v>
+        <v>-54448311.09</v>
       </c>
       <c r="L5" t="n">
-        <v>-114938871.84</v>
+        <v>-590274635.72</v>
       </c>
       <c r="M5" t="n">
-        <v>-558861792.78</v>
+        <v>-214598815.94</v>
       </c>
       <c r="N5" t="n">
-        <v>-558861792.78</v>
+        <v>-214598815.94</v>
       </c>
       <c r="O5" t="n">
-        <v>-767496812.4400001</v>
+        <v>-372490063.01</v>
       </c>
       <c r="P5" t="n">
-        <v>208635019.66</v>
+        <v>157891247.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>-391118134.34</v>
+        <v>-1266870501.05</v>
       </c>
       <c r="R5" t="n">
-        <v>-1062757.21</v>
+        <v>-1063079945.8</v>
       </c>
       <c r="S5" t="n">
-        <v>24776335</v>
+        <v>59004716.61</v>
       </c>
       <c r="T5" t="n">
-        <v>24776335</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
+        <v>59004716.61</v>
+      </c>
+      <c r="U5" t="n">
+        <v>52984227.83</v>
+      </c>
+      <c r="V5" t="n">
+        <v>52984227.83</v>
+      </c>
       <c r="W5" t="n">
-        <v>-414831712.13</v>
+        <v>-315779499.69</v>
       </c>
       <c r="X5" t="n">
-        <v>8749093.9</v>
+        <v>808387.5699999999</v>
       </c>
       <c r="Y5" t="n">
-        <v>-423580806.03</v>
+        <v>-316587887.26</v>
       </c>
       <c r="Z5" t="n">
-        <v>1192512797.99</v>
+        <v>1467379051.44</v>
       </c>
       <c r="AA5" t="n">
-        <v>-952713015.46</v>
+        <v>-90360545.59999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>-10897067.6</v>
+        <v>23016159.43</v>
       </c>
       <c r="AC5" t="n">
-        <v>912132030.95</v>
+        <v>-984041077.35</v>
       </c>
       <c r="AD5" t="n">
-        <v>-330946200.17</v>
+        <v>361526633.97</v>
       </c>
       <c r="AE5" t="n">
-        <v>-1523001778.64</v>
+        <v>509137738.35</v>
       </c>
       <c r="AF5" t="n">
-        <v>62879146.12</v>
+        <v>27917705.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>175328031.64</v>
+        <v>234926567.64</v>
       </c>
       <c r="AH5" t="n">
-        <v>130607647.32</v>
+        <v>78024842.54000001</v>
       </c>
       <c r="AI5" t="n">
-        <v>44720384.32</v>
+        <v>156901725.1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-80003701.62</v>
+        <v>-39174036.16</v>
       </c>
       <c r="AK5" t="n">
-        <v>-3656078.81</v>
+        <v>-324684.49</v>
       </c>
       <c r="AL5" t="n">
-        <v>1983992310.11</v>
+        <v>1185418098.61</v>
       </c>
       <c r="AM5" t="n">
-        <v>1192512797.99</v>
+        <v>1467379051.44</v>
       </c>
       <c r="AN5" t="n">
-        <v>-474563335.57</v>
+        <v>-462047695.38</v>
       </c>
       <c r="AO5" t="n">
-        <v>-3201966417.79</v>
+        <v>-3978902746.19</v>
       </c>
       <c r="AP5" t="n">
-        <v>-341404649.42</v>
+        <v>-680253005.49</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-670868619.01</v>
+        <v>-1504477178.46</v>
       </c>
       <c r="AR5" t="n">
-        <v>-2189693149.36</v>
+        <v>-1794172562.24</v>
       </c>
       <c r="AS5" t="n">
-        <v>4869042551.35</v>
+        <v>5908329493.01</v>
       </c>
       <c r="AT5" t="n">
-        <v>198331280.73</v>
+        <v>280362656.6</v>
       </c>
       <c r="AU5" t="n">
-        <v>4670711270.62</v>
+        <v>5627966836.41</v>
       </c>
     </row>
   </sheetData>
@@ -3414,7 +3414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FI2"/>
+  <dimension ref="A1:FG2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3885,360 +3885,350 @@
       </c>
       <c r="CP1" t="inlineStr">
         <is>
-          <t>recommendationMean</t>
+          <t>recommendationKey</t>
         </is>
       </c>
       <c r="CQ1" t="inlineStr">
         <is>
-          <t>recommendationKey</t>
+          <t>numberOfAnalystOpinions</t>
         </is>
       </c>
       <c r="CR1" t="inlineStr">
         <is>
-          <t>numberOfAnalystOpinions</t>
+          <t>totalCash</t>
         </is>
       </c>
       <c r="CS1" t="inlineStr">
         <is>
-          <t>totalCash</t>
+          <t>totalCashPerShare</t>
         </is>
       </c>
       <c r="CT1" t="inlineStr">
         <is>
-          <t>totalCashPerShare</t>
+          <t>ebitda</t>
         </is>
       </c>
       <c r="CU1" t="inlineStr">
         <is>
-          <t>ebitda</t>
+          <t>totalDebt</t>
         </is>
       </c>
       <c r="CV1" t="inlineStr">
         <is>
-          <t>totalDebt</t>
+          <t>quickRatio</t>
         </is>
       </c>
       <c r="CW1" t="inlineStr">
         <is>
-          <t>quickRatio</t>
+          <t>currentRatio</t>
         </is>
       </c>
       <c r="CX1" t="inlineStr">
         <is>
-          <t>currentRatio</t>
+          <t>totalRevenue</t>
         </is>
       </c>
       <c r="CY1" t="inlineStr">
         <is>
-          <t>totalRevenue</t>
+          <t>debtToEquity</t>
         </is>
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
-          <t>debtToEquity</t>
+          <t>revenuePerShare</t>
         </is>
       </c>
       <c r="DA1" t="inlineStr">
         <is>
-          <t>revenuePerShare</t>
+          <t>returnOnAssets</t>
         </is>
       </c>
       <c r="DB1" t="inlineStr">
         <is>
-          <t>returnOnAssets</t>
+          <t>returnOnEquity</t>
         </is>
       </c>
       <c r="DC1" t="inlineStr">
         <is>
-          <t>returnOnEquity</t>
+          <t>grossProfits</t>
         </is>
       </c>
       <c r="DD1" t="inlineStr">
         <is>
-          <t>grossProfits</t>
+          <t>freeCashflow</t>
         </is>
       </c>
       <c r="DE1" t="inlineStr">
         <is>
-          <t>freeCashflow</t>
+          <t>operatingCashflow</t>
         </is>
       </c>
       <c r="DF1" t="inlineStr">
         <is>
-          <t>operatingCashflow</t>
+          <t>earningsGrowth</t>
         </is>
       </c>
       <c r="DG1" t="inlineStr">
         <is>
-          <t>earningsGrowth</t>
+          <t>revenueGrowth</t>
         </is>
       </c>
       <c r="DH1" t="inlineStr">
         <is>
-          <t>revenueGrowth</t>
+          <t>grossMargins</t>
         </is>
       </c>
       <c r="DI1" t="inlineStr">
         <is>
-          <t>grossMargins</t>
+          <t>ebitdaMargins</t>
         </is>
       </c>
       <c r="DJ1" t="inlineStr">
         <is>
-          <t>ebitdaMargins</t>
+          <t>operatingMargins</t>
         </is>
       </c>
       <c r="DK1" t="inlineStr">
         <is>
-          <t>operatingMargins</t>
+          <t>financialCurrency</t>
         </is>
       </c>
       <c r="DL1" t="inlineStr">
         <is>
-          <t>financialCurrency</t>
+          <t>symbol</t>
         </is>
       </c>
       <c r="DM1" t="inlineStr">
         <is>
-          <t>symbol</t>
+          <t>language</t>
         </is>
       </c>
       <c r="DN1" t="inlineStr">
         <is>
-          <t>language</t>
+          <t>region</t>
         </is>
       </c>
       <c r="DO1" t="inlineStr">
         <is>
-          <t>region</t>
+          <t>typeDisp</t>
         </is>
       </c>
       <c r="DP1" t="inlineStr">
         <is>
-          <t>typeDisp</t>
+          <t>quoteSourceName</t>
         </is>
       </c>
       <c r="DQ1" t="inlineStr">
         <is>
-          <t>quoteSourceName</t>
+          <t>triggerable</t>
         </is>
       </c>
       <c r="DR1" t="inlineStr">
         <is>
-          <t>triggerable</t>
+          <t>customPriceAlertConfidence</t>
         </is>
       </c>
       <c r="DS1" t="inlineStr">
         <is>
-          <t>customPriceAlertConfidence</t>
+          <t>marketState</t>
         </is>
       </c>
       <c r="DT1" t="inlineStr">
         <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>averageDailyVolume3Month</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChange</t>
+        </is>
+      </c>
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekLowChangePercent</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekRange</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChange</t>
+        </is>
+      </c>
+      <c r="ED1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekHighChangePercent</t>
+        </is>
+      </c>
+      <c r="EE1" t="inlineStr">
+        <is>
+          <t>fiftyTwoWeekChangePercent</t>
+        </is>
+      </c>
+      <c r="EF1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EG1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EH1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FA1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EE1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EF1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>averageDailyVolume3Month</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChange</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekLowChangePercent</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekRange</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChange</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekHighChangePercent</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>fiftyTwoWeekChangePercent</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FA1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FB1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FC1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FD1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FE1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="FF1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
       <c r="FG1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="FH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="FI1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -4315,7 +4305,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Ms. Qiuping  Yang CPA', 'age': 51, 'title': 'CFO &amp; Financial Director', 'yearBorn': 1974, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Chao  Yue', 'age': 42, 'title': 'Vice President', 'yearBorn': 1983, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Tianchi  Li', 'age': 57, 'title': 'President &amp; Director', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Dianhong  Zhang', 'title': 'Head of Accounting Organization &amp; Accounting Supervisor', 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Xiaodan  Tong', 'age': 52, 'title': 'Board Secretary', 'yearBorn': 1973, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ying Bin  Zhai', 'age': 57, 'title': 'Vice President', 'yearBorn': 1968, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -4331,10 +4321,10 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U2" t="n">
-        <v>1777593600</v>
+        <v>1780531200</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -4348,28 +4338,28 @@
         <v>2</v>
       </c>
       <c r="Y2" t="n">
-        <v>86.3</v>
+        <v>80.39</v>
       </c>
       <c r="Z2" t="n">
-        <v>78.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AA2" t="n">
-        <v>78.51000000000001</v>
+        <v>79.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>86.53</v>
+        <v>82.48</v>
       </c>
       <c r="AC2" t="n">
-        <v>86.3</v>
+        <v>80.39</v>
       </c>
       <c r="AD2" t="n">
-        <v>78.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>78.51000000000001</v>
+        <v>79.98</v>
       </c>
       <c r="AF2" t="n">
-        <v>86.53</v>
+        <v>82.48</v>
       </c>
       <c r="AG2" t="n">
         <v>0.21</v>
@@ -4387,34 +4377,34 @@
         <v>0.1</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.452</v>
+        <v>0.425</v>
       </c>
       <c r="AM2" t="n">
-        <v>40.459183</v>
+        <v>41.816326</v>
       </c>
       <c r="AN2" t="n">
-        <v>27.922537</v>
+        <v>28.859156</v>
       </c>
       <c r="AO2" t="n">
-        <v>66266590</v>
+        <v>43474278</v>
       </c>
       <c r="AP2" t="n">
-        <v>66266590</v>
+        <v>43474278</v>
       </c>
       <c r="AQ2" t="n">
-        <v>25500596</v>
+        <v>29658024</v>
       </c>
       <c r="AR2" t="n">
-        <v>51736629</v>
+        <v>31263216</v>
       </c>
       <c r="AS2" t="n">
-        <v>51736629</v>
+        <v>31263216</v>
       </c>
       <c r="AT2" t="n">
-        <v>79.55</v>
+        <v>81.93000000000001</v>
       </c>
       <c r="AU2" t="n">
-        <v>79.56</v>
+        <v>81.95</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
@@ -4423,10 +4413,10 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>67375525888</v>
+        <v>69635530752</v>
       </c>
       <c r="AY2" t="n">
-        <v>67375525141</v>
+        <v>68301620001</v>
       </c>
       <c r="AZ2" t="n">
         <v>61.52</v>
@@ -4441,19 +4431,19 @@
         <v>1.111113</v>
       </c>
       <c r="BD2" t="n">
-        <v>10.179277</v>
+        <v>10.520725</v>
       </c>
       <c r="BE2" t="n">
-        <v>74.2328</v>
+        <v>76.43000000000001</v>
       </c>
       <c r="BF2" t="n">
-        <v>78.3078</v>
+        <v>78.07545</v>
       </c>
       <c r="BG2" t="n">
         <v>0.31</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0035921205</v>
+        <v>0.0038562012</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
@@ -4464,7 +4454,7 @@
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>64761102336</v>
+        <v>66995879936</v>
       </c>
       <c r="BL2" t="n">
         <v>0.24961</v>
@@ -4479,7 +4469,7 @@
         <v>0.30278</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.11415</v>
+        <v>0.114580005</v>
       </c>
       <c r="BQ2" t="n">
         <v>849628312</v>
@@ -4488,7 +4478,7 @@
         <v>16.783</v>
       </c>
       <c r="BS2" t="n">
-        <v>4.7250195</v>
+        <v>4.883513</v>
       </c>
       <c r="BT2" t="n">
         <v>1767139200</v>
@@ -4523,16 +4513,16 @@
         <v>1661299200</v>
       </c>
       <c r="CD2" t="n">
-        <v>9.784000000000001</v>
+        <v>10.122</v>
       </c>
       <c r="CE2" t="n">
-        <v>38.136</v>
+        <v>39.452</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.23443341</v>
+        <v>0.28316045</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CH2" t="n">
         <v>0.21</v>
@@ -4546,7 +4536,7 @@
         </is>
       </c>
       <c r="CK2" t="n">
-        <v>79.3</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="CL2" t="n">
         <v>120.52</v>
@@ -4560,262 +4550,254 @@
       <c r="CO2" t="n">
         <v>109</v>
       </c>
-      <c r="CP2" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="CQ2" t="inlineStr">
-        <is>
-          <t>buy</t>
-        </is>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="CQ2" t="n">
+        <v>3</v>
       </c>
       <c r="CR2" t="n">
-        <v>3</v>
+        <v>3781782528</v>
       </c>
       <c r="CS2" t="n">
-        <v>3781782528</v>
+        <v>4.501</v>
       </c>
       <c r="CT2" t="n">
-        <v>4.501</v>
+        <v>1698166272</v>
       </c>
       <c r="CU2" t="n">
-        <v>1698166272</v>
+        <v>1827986048</v>
       </c>
       <c r="CV2" t="n">
-        <v>1827986048</v>
+        <v>3.976</v>
       </c>
       <c r="CW2" t="n">
-        <v>3.976</v>
+        <v>5.053</v>
       </c>
       <c r="CX2" t="n">
-        <v>5.053</v>
+        <v>6618890752</v>
       </c>
       <c r="CY2" t="n">
-        <v>6618890752</v>
+        <v>12.881</v>
       </c>
       <c r="CZ2" t="n">
-        <v>12.881</v>
+        <v>7.869</v>
       </c>
       <c r="DA2" t="n">
-        <v>7.869</v>
+        <v>0.05218</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.05218</v>
+        <v>0.12356</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.12356</v>
+        <v>3624407296</v>
       </c>
       <c r="DD2" t="n">
-        <v>3624407296</v>
+        <v>-740231744</v>
       </c>
       <c r="DE2" t="n">
-        <v>-740231744</v>
+        <v>633786240</v>
       </c>
       <c r="DF2" t="n">
-        <v>633786240</v>
+        <v>1.804</v>
       </c>
       <c r="DG2" t="n">
-        <v>1.804</v>
+        <v>0.461</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.461</v>
+        <v>0.54759</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.54759</v>
+        <v>0.25656</v>
       </c>
       <c r="DJ2" t="n">
-        <v>0.25656</v>
-      </c>
-      <c r="DK2" t="n">
         <v>0.21173</v>
       </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
       <c r="DL2" t="inlineStr">
         <is>
-          <t>CNY</t>
+          <t>002049.SZ</t>
         </is>
       </c>
       <c r="DM2" t="inlineStr">
         <is>
-          <t>002049.SZ</t>
+          <t>en-US</t>
         </is>
       </c>
       <c r="DN2" t="inlineStr">
         <is>
-          <t>en-US</t>
+          <t>US</t>
         </is>
       </c>
       <c r="DO2" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Equity</t>
         </is>
       </c>
       <c r="DP2" t="inlineStr">
         <is>
-          <t>Equity</t>
-        </is>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
           <t>Delayed Quote</t>
         </is>
       </c>
-      <c r="DR2" t="b">
+      <c r="DQ2" t="b">
         <v>0</v>
       </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
       <c r="DS2" t="inlineStr">
         <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="DT2" t="n">
-        <v>-8.111238999999999</v>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
       </c>
       <c r="DU2" t="n">
-        <v>79.3</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
+        <v>1118021400000</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1.5699997</v>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
-          <t>finmb_22277502</t>
+          <t>79.98 - 82.48</t>
         </is>
       </c>
       <c r="DX2" t="inlineStr">
         <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="DY2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
+          <t>Shenzhen</t>
+        </is>
+      </c>
+      <c r="DY2" t="n">
+        <v>29658024</v>
       </c>
       <c r="DZ2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>UNIGROUP GUOXIN MICROELECTRONIC</t>
-        </is>
+        <v>20.439999</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.33224964</v>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>61.52 - 94.83</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>-12.870003</v>
       </c>
       <c r="ED2" t="n">
-        <v>0.99220276</v>
+        <v>-0.13571657</v>
       </c>
       <c r="EE2" t="n">
-        <v>0.012670549</v>
+        <v>28.316044</v>
       </c>
       <c r="EF2" t="n">
-        <v>15</v>
+        <v>1745924340</v>
       </c>
       <c r="EG2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EH2" t="inlineStr">
-        <is>
-          <t>1.8 - Buy</t>
-        </is>
-      </c>
-      <c r="EI2" t="b">
-        <v>0</v>
+        <v>1745924340</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>1746774000</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1746774000</v>
       </c>
       <c r="EJ2" t="b">
         <v>0</v>
       </c>
       <c r="EK2" t="n">
-        <v>1118021400000</v>
+        <v>1.96</v>
       </c>
       <c r="EL2" t="n">
-        <v>-7</v>
+        <v>2.84</v>
       </c>
       <c r="EM2" t="inlineStr">
         <is>
-          <t>78.51 - 86.53</t>
+          <t>UNIGROUP GUOXIN MICROELECTRONIC</t>
         </is>
       </c>
       <c r="EN2" t="inlineStr">
         <is>
-          <t>Shenzhen</t>
-        </is>
-      </c>
-      <c r="EO2" t="n">
-        <v>25500596</v>
+          <t>Unigroup Guoxin Microelectronics Co., Ltd.</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="EP2" t="n">
-        <v>17.780003</v>
+        <v>1782111855</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0.28901175</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>61.52 - 94.83</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>-15.529999</v>
-      </c>
-      <c r="ET2" t="n">
-        <v>-0.16376673</v>
-      </c>
-      <c r="EU2" t="n">
-        <v>23.44334</v>
-      </c>
-      <c r="EV2" t="n">
-        <v>1745924340</v>
+        <v>1.9529787</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>81.95999999999999</v>
+      </c>
+      <c r="ES2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="ET2" t="inlineStr">
+        <is>
+          <t>finmb_22277502</t>
+        </is>
+      </c>
+      <c r="EU2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="EV2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
       </c>
       <c r="EW2" t="n">
-        <v>1745924340</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1746774000</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1746774000</v>
-      </c>
-      <c r="EZ2" t="b">
+        <v>28800000</v>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="EY2" t="b">
         <v>0</v>
       </c>
+      <c r="EZ2" t="n">
+        <v>5.529999</v>
+      </c>
       <c r="FA2" t="n">
-        <v>1.96</v>
+        <v>0.07235377</v>
       </c>
       <c r="FB2" t="n">
-        <v>2.84</v>
+        <v>3.884552</v>
       </c>
       <c r="FC2" t="n">
-        <v>5.0671997</v>
+        <v>0.049753822</v>
       </c>
       <c r="FD2" t="n">
-        <v>0.06826092</v>
-      </c>
-      <c r="FE2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="FF2" t="n">
-        <v>1780038264</v>
-      </c>
-      <c r="FG2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="FH2" t="inlineStr">
-        <is>
-          <t>Unigroup Guoxin Microelectronics Co., Ltd.</t>
-        </is>
-      </c>
-      <c r="FI2" t="inlineStr"/>
+        <v>15</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FF2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FG2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
